--- a/docs/downloads/11/tbl_degats_champs_riz_alaotra_tous.xlsx
+++ b/docs/downloads/11/tbl_degats_champs_riz_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,17 +418,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -442,17 +442,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>31.6</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -461,46 +461,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="D5">
-        <v>60</v>
+        <v>11.8</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>76.5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>68.40000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="E6">
-        <v>31.6</v>
+        <v>16.7</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -509,22 +509,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Facteur humain</t>
         </is>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -533,22 +533,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -557,84 +557,84 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="D9">
-        <v>75</v>
+        <v>15.4</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C10">
-        <v>5.9</v>
+        <v>16.7</v>
       </c>
       <c r="D10">
-        <v>11.8</v>
+        <v>66.7</v>
       </c>
       <c r="E10">
-        <v>76.5</v>
+        <v>16.7</v>
       </c>
       <c r="F10">
-        <v>5.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C11">
-        <v>50</v>
+        <v>9.5</v>
       </c>
       <c r="D11">
-        <v>33.3</v>
+        <v>9.5</v>
       </c>
       <c r="E11">
-        <v>16.7</v>
+        <v>76.2</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C12">
@@ -653,22 +653,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Facteur humain</t>
         </is>
       </c>
       <c r="C13">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -677,22 +677,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C14">
-        <v>50</v>
+        <v>7.7</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>46.2</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>46.2</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -701,46 +701,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C15">
-        <v>3.8</v>
+        <v>66.7</v>
       </c>
       <c r="D15">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>76.90000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="F15">
-        <v>3.8</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C16">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>25</v>
+        <v>83.3</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -749,46 +749,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Inondation</t>
         </is>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C18">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -797,94 +797,94 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C19">
-        <v>16.7</v>
+        <v>10.6</v>
       </c>
       <c r="D19">
-        <v>66.7</v>
+        <v>12.8</v>
       </c>
       <c r="E19">
-        <v>16.7</v>
+        <v>55.3</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Inondation</t>
         </is>
       </c>
       <c r="C20">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="D20">
-        <v>9.5</v>
+        <v>47.6</v>
       </c>
       <c r="E20">
-        <v>76.2</v>
+        <v>47.6</v>
       </c>
       <c r="F20">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C21">
-        <v>100</v>
+        <v>3.3</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -893,7 +893,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -905,34 +905,34 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="E23">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C24">
-        <v>7.7</v>
+        <v>37.5</v>
       </c>
       <c r="D24">
-        <v>46.2</v>
+        <v>62.5</v>
       </c>
       <c r="E24">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -941,118 +941,118 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C25">
-        <v>66.7</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>33.3</v>
+        <v>22.4</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>53.1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Autres</t>
         </is>
       </c>
       <c r="C26">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E26">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>71.2</v>
       </c>
       <c r="D27">
-        <v>83.3</v>
+        <v>13.5</v>
       </c>
       <c r="E27">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Inondation</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>37.5</v>
+        <v>70</v>
       </c>
       <c r="E28">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Facteur humain</t>
         </is>
       </c>
       <c r="C29">
-        <v>55.6</v>
+        <v>94.3</v>
       </c>
       <c r="D29">
-        <v>33.3</v>
+        <v>2.9</v>
       </c>
       <c r="E29">
-        <v>11.1</v>
+        <v>2.9</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1061,70 +1061,70 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Grêle</t>
         </is>
       </c>
       <c r="C30">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>12.8</v>
+        <v>22.2</v>
       </c>
       <c r="E30">
-        <v>55.3</v>
+        <v>77.8</v>
       </c>
       <c r="F30">
-        <v>21.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Inondation</t>
         </is>
       </c>
       <c r="C31">
-        <v>75</v>
+        <v>2.6</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>46.2</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grêle</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="D32">
-        <v>33.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E32">
-        <v>66.7</v>
+        <v>4.2</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1133,22 +1133,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Inondation</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C33">
-        <v>4.8</v>
+        <v>29.3</v>
       </c>
       <c r="D33">
-        <v>47.6</v>
+        <v>58.5</v>
       </c>
       <c r="E33">
-        <v>47.6</v>
+        <v>12.2</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1157,456 +1157,24 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C34">
-        <v>33.3</v>
+        <v>5.4</v>
       </c>
       <c r="D34">
-        <v>66.7</v>
+        <v>23</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>58.6</v>
       </c>
       <c r="F34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Rats</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>100</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Sécheresse</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>3.3</v>
-      </c>
-      <c r="D36">
-        <v>23.3</v>
-      </c>
-      <c r="E36">
-        <v>56.7</v>
-      </c>
-      <c r="F36">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Autres bestioles</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>83.3</v>
-      </c>
-      <c r="D37">
-        <v>11.1</v>
-      </c>
-      <c r="E37">
-        <v>5.6</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Facteur humain</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>100</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Grêle</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39">
-        <v>100</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Inondation</t>
-        </is>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>33.3</v>
-      </c>
-      <c r="E40">
-        <v>50</v>
-      </c>
-      <c r="F40">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Maladie</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>100</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Rats</t>
-        </is>
-      </c>
-      <c r="C42">
-        <v>37.5</v>
-      </c>
-      <c r="D42">
-        <v>62.5</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Sécheresse</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>2</v>
-      </c>
-      <c r="D43">
-        <v>22.4</v>
-      </c>
-      <c r="E43">
-        <v>53.1</v>
-      </c>
-      <c r="F43">
-        <v>22.4</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>80</v>
-      </c>
-      <c r="D44">
-        <v>20</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Autres bestioles</t>
-        </is>
-      </c>
-      <c r="C45">
-        <v>71.2</v>
-      </c>
-      <c r="D45">
-        <v>13.5</v>
-      </c>
-      <c r="E45">
-        <v>13.5</v>
-      </c>
-      <c r="F45">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Cyclone</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>10</v>
-      </c>
-      <c r="D46">
-        <v>70</v>
-      </c>
-      <c r="E46">
-        <v>20</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Facteur humain</t>
-        </is>
-      </c>
-      <c r="C47">
-        <v>94.3</v>
-      </c>
-      <c r="D47">
-        <v>2.9</v>
-      </c>
-      <c r="E47">
-        <v>2.9</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Grêle</t>
-        </is>
-      </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48">
-        <v>22.2</v>
-      </c>
-      <c r="E48">
-        <v>77.8</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Inondation</t>
-        </is>
-      </c>
-      <c r="C49">
-        <v>2.6</v>
-      </c>
-      <c r="D49">
-        <v>43.6</v>
-      </c>
-      <c r="E49">
-        <v>46.2</v>
-      </c>
-      <c r="F49">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Maladie</t>
-        </is>
-      </c>
-      <c r="C50">
-        <v>87.5</v>
-      </c>
-      <c r="D50">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E50">
-        <v>4.2</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Rats</t>
-        </is>
-      </c>
-      <c r="C51">
-        <v>29.3</v>
-      </c>
-      <c r="D51">
-        <v>58.5</v>
-      </c>
-      <c r="E51">
-        <v>12.2</v>
-      </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Sécheresse</t>
-        </is>
-      </c>
-      <c r="C52">
-        <v>5.4</v>
-      </c>
-      <c r="D52">
-        <v>23</v>
-      </c>
-      <c r="E52">
-        <v>58.6</v>
-      </c>
-      <c r="F52">
         <v>13.1</v>
       </c>
     </row>

--- a/docs/downloads/11/tbl_degats_champs_riz_alaotra_tous.xlsx
+++ b/docs/downloads/11/tbl_degats_champs_riz_alaotra_tous.xlsx
@@ -389,7 +389,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -413,7 +413,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -437,7 +437,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -461,7 +461,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -509,7 +509,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -605,7 +605,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1037,7 +1037,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1061,7 +1061,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1085,7 +1085,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
